--- a/testData/Credentials.xlsx
+++ b/testData/Credentials.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajes\OneDrive\Desktop\Ucovy Saucedemo\Ecommerce-Framework-Sauce-demo\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajes\OneDrive\Desktop\SauceDemo\Ecommerce-Framework-Sauce-demo\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42400455-6102-43B1-A392-8FE4474CB88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78522422-ADA7-4296-90F4-8BFCF2F89689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EEB2B1FE-EE1D-4063-9A05-5CFCEA4B0662}"/>
   </bookViews>
